--- a/Spar/Claims management/Contacts.xlsx
+++ b/Spar/Claims management/Contacts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gstim\.openclaw\workspace\Spar\Claims management\DC Claims matching 2026-06-26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gstim\.openclaw\workspace\Spar\Claims management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF914C8B-9195-47D2-9B08-9DF4C1BF51EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92989D8D-58F6-442C-9942-0AC0778D32C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEAC7017-C917-4556-A2F6-62D507AC22F4}"/>
   </bookViews>
@@ -39,35 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
-  <si>
-    <t>bennienothnagel@spar.co.za</t>
-  </si>
-  <si>
-    <t>brandondaniels@spar.co.za</t>
-  </si>
-  <si>
-    <t>wesley.falkner@spar.co.za</t>
-  </si>
-  <si>
-    <t>anton.marais@spar.co.za</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
   <si>
     <t>zelnavandeventer@spar.co.za</t>
   </si>
   <si>
-    <t>michelle.laubser@spar.co.za</t>
-  </si>
-  <si>
     <t>james.bronkhast@spar.co.za</t>
   </si>
   <si>
-    <t>leslie.naiker@spar.co.za</t>
-  </si>
-  <si>
-    <t>ustonlopez@spar.co.za</t>
-  </si>
-  <si>
     <t>Shorts</t>
   </si>
   <si>
@@ -107,77 +86,96 @@
     <t>Department</t>
   </si>
   <si>
-    <t>elton.barnard@spar.co.za</t>
-  </si>
-  <si>
-    <t>phinde.ntsantsa@spar.co.za</t>
-  </si>
-  <si>
     <t>CC</t>
   </si>
   <si>
-    <t>gadija.jacobs@spar.co.za</t>
-  </si>
-  <si>
-    <t>asanda.mnukwa@spar.co.za</t>
-  </si>
-  <si>
-    <t>simphiwe.thandela@spar.co.za</t>
-  </si>
-  <si>
     <t>Assets?</t>
   </si>
   <si>
     <t>Dry Goods</t>
   </si>
   <si>
-    <t>021 690 0000</t>
-  </si>
-  <si>
-    <t>Phone no</t>
-  </si>
-  <si>
-    <t>jean.japtha@spar.co.za</t>
-  </si>
-  <si>
-    <t>Hash code</t>
+    <t>Gateway</t>
+  </si>
+  <si>
+    <t>Claims</t>
+  </si>
+  <si>
+    <t>Bennie.Nothnagel@spar.co.za</t>
+  </si>
+  <si>
+    <t>Anton.Marais@spar.co.za</t>
+  </si>
+  <si>
+    <t>Brandon.Daniels@spar.co.za</t>
+  </si>
+  <si>
+    <t>Leslie.Naiker@spar.co.za</t>
+  </si>
+  <si>
+    <t>Michelle.Laubscher@spar.co.za</t>
+  </si>
+  <si>
+    <t>Phakama.Mvandaba@spar.co.za</t>
+  </si>
+  <si>
+    <t>Uston.Lopez@spar.co.za</t>
+  </si>
+  <si>
+    <t>Wesley.Falconer@spar.co.za</t>
+  </si>
+  <si>
+    <t>Phinde.Ntsantsa@spar.co.za</t>
+  </si>
+  <si>
+    <t>Jean.Japtha@spar.co.za</t>
+  </si>
+  <si>
+    <t>Elton.Barnard@spar.co.za</t>
+  </si>
+  <si>
+    <t> Gadija.Jacobs@spar.co.za</t>
+  </si>
+  <si>
+    <t>Ernest.Kempshall@spar.co.za</t>
+  </si>
+  <si>
+    <t>Lisa.Forrest@spar.co.za</t>
+  </si>
+  <si>
+    <t>Asanda.Mnukwa@spar.co.za</t>
+  </si>
+  <si>
+    <t>Simphiwe.Thandela@spar.co.za</t>
+  </si>
+  <si>
+    <t>Buyer</t>
+  </si>
+  <si>
+    <t>Lauren.Jankielsohn@spar.co.za</t>
+  </si>
+  <si>
+    <t>0216900283</t>
+  </si>
+  <si>
+    <t>SPAR DC</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>0219600000</t>
   </si>
   <si>
     <t>7314#</t>
-  </si>
-  <si>
-    <t>ernest.kempshall@spar.co.za</t>
-  </si>
-  <si>
-    <t>Gateway</t>
-  </si>
-  <si>
-    <t>lisa.forrest@spar.co.za</t>
-  </si>
-  <si>
-    <t>Claims</t>
-  </si>
-  <si>
-    <t>phakama.mvandaba@spar.co.za</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -192,16 +190,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -216,7 +233,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -231,7 +248,7 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -249,7 +266,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -264,7 +281,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -276,10 +293,8 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -291,7 +306,35 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -302,17 +345,39 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -648,216 +713,224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FC3907-B62E-4971-B3A8-2D653077C6D6}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="B1:D25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.453125" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="C21" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C24" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B25" s="10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" t="s">
-        <v>34</v>
+      <c r="C25" s="9" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B12">
-    <sortCondition ref="A2:A12"/>
-  </sortState>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{263770FA-B12A-4F2C-AA6D-7395A5FE50F3}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{8AE0D521-F15C-42EA-AF75-FB5F3801D50F}"/>
-    <hyperlink ref="A8" r:id="rId3" xr:uid="{3C88A9BA-D950-4404-A48D-C31151207CA5}"/>
-    <hyperlink ref="A10" r:id="rId4" xr:uid="{734062FF-30B2-41FE-AD47-5948DF3565DE}"/>
-    <hyperlink ref="A2" r:id="rId5" xr:uid="{E42EC9BF-7A46-43F3-9C3D-AC5FDA4D4A8E}"/>
-    <hyperlink ref="A11" r:id="rId6" xr:uid="{F518DC71-CE77-48EC-A1AA-76974F7C7A7D}"/>
-    <hyperlink ref="A7" r:id="rId7" xr:uid="{EF09E230-4BD9-4414-AA55-85BBA4A245C5}"/>
-    <hyperlink ref="A5" r:id="rId8" xr:uid="{081CD6ED-76BC-410E-B54C-E2A9FE4FB6C5}"/>
-    <hyperlink ref="A6" r:id="rId9" xr:uid="{0828E127-4DA2-4421-9936-5D3DEDD4764D}"/>
-    <hyperlink ref="A9" r:id="rId10" xr:uid="{448EC057-3E0A-4178-9CCE-D9DD630E1670}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{9BE17EC3-7904-4C04-B9DE-26B2ADD03147}"/>
-    <hyperlink ref="A14" r:id="rId12" xr:uid="{EA2237A7-CB34-4D7D-AC5D-D84269451426}"/>
-    <hyperlink ref="A15" r:id="rId13" xr:uid="{665B532E-BB18-433D-9023-1DBE7829C9A2}"/>
-    <hyperlink ref="A13" r:id="rId14" xr:uid="{9D7EAF3E-014C-42C2-80C8-D5494E0C71BB}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{A9BD7FC7-A4F6-439F-8920-6F18B0BB8CC0}"/>
-    <hyperlink ref="A19" r:id="rId16" xr:uid="{51A0F87C-5878-4242-A5A4-E6426CA6CA7B}"/>
-    <hyperlink ref="A20" r:id="rId17" xr:uid="{744AE7D3-7A35-4CDC-85BB-C377C17B0197}"/>
-    <hyperlink ref="A17" r:id="rId18" xr:uid="{107653C6-37B9-4784-A122-928A30915B5D}"/>
-    <hyperlink ref="A18" r:id="rId19" xr:uid="{B829A7DD-7C64-49E3-B6E6-18CCC592FA29}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{D1FD161B-4AD4-4E44-90A8-44BAB7FE35DD}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{DB271FBA-8F46-4ACE-969E-E9BE1BA21C52}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{8F3066B8-CE54-4E2B-A8B1-2777FE1FB0BA}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{34473290-A6E9-4342-B2CF-B25DA0DFBB0D}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{D42F3283-940B-4685-9D50-AAB2469406F6}"/>
+    <hyperlink ref="C9" r:id="rId6" xr:uid="{705AAFDB-1B94-4EE0-8998-DC463CAD35FF}"/>
+    <hyperlink ref="C10" r:id="rId7" xr:uid="{08ECB163-F56E-4350-A30B-7A437CBF0801}"/>
+    <hyperlink ref="C14" r:id="rId8" xr:uid="{FF7FD87A-FDDB-4558-A4CE-2DD44EDCB0D5}"/>
+    <hyperlink ref="C15" r:id="rId9" xr:uid="{A313561E-10CB-4C99-977D-E8A3B6245F26}"/>
+    <hyperlink ref="C16" r:id="rId10" xr:uid="{9511C8CD-3FD8-4786-95CF-F3DC0D0FFF1F}"/>
+    <hyperlink ref="C17" r:id="rId11" display="mailto:Gadija.Jacobs@spar.co.za" xr:uid="{6DC053A5-37FF-4262-8B89-86ABC6A72DEB}"/>
+    <hyperlink ref="C18" r:id="rId12" xr:uid="{D65F4BA9-CD3B-4438-9490-62C1EFF3C683}"/>
+    <hyperlink ref="C19" r:id="rId13" xr:uid="{E91776A1-62F5-477A-9ED1-992564BF4403}"/>
+    <hyperlink ref="C20" r:id="rId14" xr:uid="{FDE693CE-0841-4E35-8AB9-5E60BE2CFD4E}"/>
+    <hyperlink ref="C21" r:id="rId15" xr:uid="{CC97301E-EF85-428D-B783-B9E4837C543D}"/>
+    <hyperlink ref="C11" r:id="rId16" xr:uid="{80A48894-97A5-4A5B-90DB-CA6D095E4CC3}"/>
+    <hyperlink ref="C6" r:id="rId17" xr:uid="{18E10C6F-236C-4DAD-805D-2809452A5740}"/>
+    <hyperlink ref="C12" r:id="rId18" xr:uid="{C93EE3BB-FF13-4CEA-B4C9-06E636A09561}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{6083177F-AA1C-4A98-93EB-4A6D72F519C5}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{6061E60D-14D0-44B5-927B-D24504FCE179}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Spar/Claims management/Contacts.xlsx
+++ b/Spar/Claims management/Contacts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gstim\.openclaw\workspace\Spar\Claims management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92989D8D-58F6-442C-9942-0AC0778D32C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBEE38B-3784-4DF6-9D8E-9E72679B8409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEAC7017-C917-4556-A2F6-62D507AC22F4}"/>
   </bookViews>
@@ -164,10 +164,10 @@
     <t>Code</t>
   </si>
   <si>
-    <t>0219600000</t>
-  </si>
-  <si>
     <t>7314#</t>
+  </si>
+  <si>
+    <t>0216900000</t>
   </si>
 </sst>
 </file>
@@ -898,7 +898,7 @@
         <v>39</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.35">
@@ -906,7 +906,7 @@
         <v>40</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Spar/Claims management/Contacts.xlsx
+++ b/Spar/Claims management/Contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gstim\.openclaw\workspace\Spar\Claims management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBEE38B-3784-4DF6-9D8E-9E72679B8409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272FAC60-629F-48A1-954C-8E31DF751063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEAC7017-C917-4556-A2F6-62D507AC22F4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>zelnavandeventer@spar.co.za</t>
   </si>
@@ -155,9 +155,6 @@
     <t>Lauren.Jankielsohn@spar.co.za</t>
   </si>
   <si>
-    <t>0216900283</t>
-  </si>
-  <si>
     <t>SPAR DC</t>
   </si>
   <si>
@@ -168,6 +165,12 @@
   </si>
   <si>
     <t>0216900000</t>
+  </si>
+  <si>
+    <t>Phone no</t>
+  </si>
+  <si>
+    <t>021 690 0283</t>
   </si>
 </sst>
 </file>
@@ -718,7 +721,7 @@
   <cols>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.453125" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -729,6 +732,9 @@
       <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="D2" s="7" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
@@ -737,6 +743,7 @@
       <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
@@ -745,6 +752,7 @@
       <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
@@ -753,6 +761,7 @@
       <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
@@ -761,6 +770,7 @@
       <c r="C6" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
@@ -769,6 +779,7 @@
       <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
@@ -777,6 +788,7 @@
       <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
@@ -785,6 +797,7 @@
       <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -793,6 +806,7 @@
       <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
@@ -801,6 +815,7 @@
       <c r="C11" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
@@ -809,6 +824,7 @@
       <c r="C12" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
@@ -817,6 +833,7 @@
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
@@ -825,8 +842,8 @@
       <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>38</v>
+      <c r="D14" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.35">
@@ -836,6 +853,7 @@
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
@@ -844,69 +862,76 @@
       <c r="C16" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="22" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="D22" s="8"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Spar/Claims management/Contacts.xlsx
+++ b/Spar/Claims management/Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gstim\.openclaw\workspace\Spar\Claims management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272FAC60-629F-48A1-954C-8E31DF751063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE2C712-D195-468D-9023-9C7E465F6240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEAC7017-C917-4556-A2F6-62D507AC22F4}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{CEAC7017-C917-4556-A2F6-62D507AC22F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>zelnavandeventer@spar.co.za</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>021 690 0283</t>
+  </si>
+  <si>
+    <t>bo</t>
   </si>
 </sst>
 </file>
@@ -716,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FC3907-B62E-4971-B3A8-2D653077C6D6}">
-  <dimension ref="B1:D25"/>
+  <dimension ref="B1:F25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -724,8 +727,8 @@
     <col min="4" max="4" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>14</v>
       </c>
@@ -736,7 +739,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
@@ -745,7 +748,7 @@
       </c>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
@@ -754,7 +757,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -763,7 +766,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
@@ -772,7 +775,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
@@ -781,7 +784,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
@@ -790,7 +793,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -799,7 +802,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
@@ -808,7 +811,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>2</v>
       </c>
@@ -817,7 +820,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +828,11 @@
         <v>0</v>
       </c>
       <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,7 +841,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
@@ -846,7 +852,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
@@ -855,7 +861,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
